--- a/client/src/resumix_client/resources/applications.xlsx
+++ b/client/src/resumix_client/resources/applications.xlsx
@@ -479,7 +479,7 @@
   <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown status" error="Pick one of: not applied, applied, wait 1st interview, wait follow up" type="list">
-      <formula1>"not applied,applied,wait 1st interview,wait follow up,discarded"</formula1>
+      <formula1>"not applied,applied,wait 1st interview,wait follow up,skip_application,candidate rejected"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/src/resumix_client/resources/applications.xlsx
+++ b/client/src/resumix_client/resources/applications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="applications" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="applications" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'applications'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'applications'!$A$1:$G$500</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,6 +65,112 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F4E4"/>
+          <bgColor rgb="00E2F4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C4E8C9"/>
+          <bgColor rgb="00C4E8C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="009EDAA5"/>
+          <bgColor rgb="009EDAA5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFE6E6"/>
+          <bgColor rgb="00FFE6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCECE"/>
+          <bgColor rgb="00FFCECE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFACAC"/>
+          <bgColor rgb="00FFACAC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0080CE8A"/>
+          <bgColor rgb="0080CE8A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="003CB44B"/>
+          <bgColor rgb="003CB44B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF9494"/>
+          <bgColor rgb="00FF9494"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF5A5A"/>
+          <bgColor rgb="00FF5A5A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F0BEBE"/>
+          <bgColor rgb="00F0BEBE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DE7373"/>
+          <bgColor rgb="00DE7373"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00CC2828"/>
+          <bgColor rgb="00CC2828"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -476,10 +582,30 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G500"/>
+  <conditionalFormatting sqref="D2:D1048576">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"waiting 1st interview"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="6">
+      <formula>"waiting 2nd interview"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="7">
+      <formula>"waiting further follow up"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="10">
+      <formula>"rejected before 1st interview"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="11">
+      <formula>"rejected after 1st interview"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="12">
+      <formula>"rejected after technical interview"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown status" error="Pick one of: not applied, applied, wait 1st interview, wait follow up" type="list">
-      <formula1>"not applied,applied,wait 1st interview,wait follow up,skip_application,candidate rejected"</formula1>
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Unknown status" error="Pick one of: not applied, applied, waiting 1st interview, waiting 2nd interview, waiting further follow up, skip_application, rejected before 1st interview, rejected after 1st interview, rejected after technical interview" type="list">
+      <formula1>"not applied,applied,waiting 1st interview,waiting 2nd interview,waiting further follow up,skip_application,rejected before 1st interview,rejected after 1st interview,rejected after technical interview"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
